--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/PENNSYLVANIA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/PENNSYLVANIA_2010.xlsx
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C84">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C601">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C658">
